--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/TEXAS_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/TEXAS_2012.xlsx
@@ -1507,7 +1507,7 @@
         <v>19</v>
       </c>
       <c r="D64">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="65">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C177">
@@ -3595,7 +3595,7 @@
         <v>19</v>
       </c>
       <c r="D180">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="181">
@@ -3811,7 +3811,7 @@
         <v>19</v>
       </c>
       <c r="D192">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="193">
@@ -3973,7 +3973,7 @@
         <v>19</v>
       </c>
       <c r="D201">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="202">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C252">
@@ -5377,7 +5377,7 @@
         <v>19</v>
       </c>
       <c r="D279">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="280">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C286">
@@ -8059,7 +8059,7 @@
         <v>19</v>
       </c>
       <c r="D428">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="429">
@@ -8419,7 +8419,7 @@
         <v>186</v>
       </c>
       <c r="D448">
-        <v>0.000965601736007</v>
+        <v>0.0009656017360070002</v>
       </c>
     </row>
     <row r="449">
@@ -9895,7 +9895,7 @@
         <v>19</v>
       </c>
       <c r="D530">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="531">
@@ -10057,7 +10057,7 @@
         <v>19</v>
       </c>
       <c r="D539">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="540">
@@ -10777,7 +10777,7 @@
         <v>19</v>
       </c>
       <c r="D579">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="580">
@@ -11371,7 +11371,7 @@
         <v>19</v>
       </c>
       <c r="D612">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="613">
@@ -13279,7 +13279,7 @@
         <v>19</v>
       </c>
       <c r="D718">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="719">
@@ -14773,7 +14773,7 @@
         <v>19</v>
       </c>
       <c r="D801">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="802">
@@ -15007,7 +15007,7 @@
         <v>19</v>
       </c>
       <c r="D814">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="815">
@@ -15061,7 +15061,7 @@
         <v>19</v>
       </c>
       <c r="D817">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="818">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C907">
@@ -18877,7 +18877,7 @@
         <v>19</v>
       </c>
       <c r="D1029">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1030">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1076">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1077">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1133">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1141">
@@ -22567,7 +22567,7 @@
         <v>19</v>
       </c>
       <c r="D1234">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1235">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1239">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1333">
@@ -25573,7 +25573,7 @@
         <v>19</v>
       </c>
       <c r="D1401">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1402">
@@ -27553,7 +27553,7 @@
         <v>1920</v>
       </c>
       <c r="D1511">
-        <v>0.009967501791035</v>
+        <v>0.009967501791035002</v>
       </c>
     </row>
     <row r="1512">
@@ -27913,7 +27913,7 @@
         <v>19</v>
       </c>
       <c r="D1531">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1532">
@@ -28471,7 +28471,7 @@
         <v>19</v>
       </c>
       <c r="D1562">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1563">
@@ -29353,7 +29353,7 @@
         <v>19</v>
       </c>
       <c r="D1611">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1612">
@@ -29533,7 +29533,7 @@
         <v>180</v>
       </c>
       <c r="D1621">
-        <v>0.00093445329291</v>
+        <v>0.0009344532929100002</v>
       </c>
     </row>
     <row r="1622">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1658">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1698">
@@ -31405,7 +31405,7 @@
         <v>19</v>
       </c>
       <c r="D1725">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1726">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="B1879" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1879">
@@ -35419,7 +35419,7 @@
         <v>19</v>
       </c>
       <c r="D1948">
-        <v>9.8636736474E-05</v>
+        <v>9.863673647400001E-05</v>
       </c>
     </row>
     <row r="1949">
